--- a/templates/ym/pl.xlsx
+++ b/templates/ym/pl.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6550"/>
+    <workbookView windowWidth="29400" windowHeight="14100"/>
   </bookViews>
   <sheets>
     <sheet name="PL" sheetId="53286" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="32">
   <si>
     <t>WEIHAI E-MAX SPORT APPARATUS CO.,LTD </t>
   </si>
@@ -45,26 +45,6 @@
   </si>
   <si>
     <t>Invoice No.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Times New Roman"/>
-        <charset val="0"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发票号</t>
-    </r>
   </si>
   <si>
     <t>MADE IN CHINA</t>
@@ -94,103 +74,7 @@
     <t>CTNS</t>
   </si>
   <si>
-    <t>括号内数值手动更新</t>
-  </si>
-  <si>
     <t>FISHING REELS (1277PCS,1001.21KGS)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>RO new PO template A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Purchasing Document"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>RO new PO template J</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Model"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>RO new PO template I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Material"</t>
-    </r>
-  </si>
-  <si>
-    <t>PO record</t>
-  </si>
-  <si>
-    <t>SK+YM箱单</t>
   </si>
   <si>
     <t>CB2500.B2</t>
@@ -241,9 +125,6 @@
     <t>PACKED IN 88 CTNS</t>
   </si>
   <si>
-    <t>箱数手动更新</t>
-  </si>
-  <si>
     <t>THERE IS NO SOLID WOOD PACKING MATERIAL IN THIS SHIPMENT.</t>
   </si>
 </sst>
@@ -269,7 +150,7 @@
     <numFmt numFmtId="186" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="187" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="77">
+  <fonts count="76">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -765,12 +646,6 @@
       <sz val="10"/>
       <name val="굴림체"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="40"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="59">
@@ -2279,9 +2154,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="184" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="267">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2592,7 +2464,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5080" y="5080"/>
-          <a:ext cx="1558925" cy="647700"/>
+          <a:ext cx="1565275" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2896,20 +2768,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:CC29"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="4.83636363636364" style="5" customWidth="1"/>
-    <col min="2" max="2" width="17.5454545454545" style="5" customWidth="1"/>
-    <col min="3" max="3" width="11.8363636363636" style="5" customWidth="1"/>
+    <col min="1" max="1" width="4.83928571428571" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.5446428571429" style="5" customWidth="1"/>
+    <col min="3" max="3" width="11.8392857142857" style="5" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="25.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9.33636363636364" style="5" customWidth="1"/>
-    <col min="7" max="7" width="10.6363636363636" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9.33928571428571" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.6339285714286" style="5" customWidth="1"/>
     <col min="8" max="8" width="9" style="5" customWidth="1"/>
-    <col min="9" max="9" width="8.33636363636364" style="5" customWidth="1"/>
-    <col min="10" max="10" width="7.33636363636364" style="6" customWidth="1"/>
-    <col min="11" max="12" width="5.66363636363636" style="6" customWidth="1"/>
-    <col min="13" max="13" width="8.33636363636364" style="7" customWidth="1"/>
+    <col min="9" max="9" width="8.33928571428571" style="5" customWidth="1"/>
+    <col min="10" max="10" width="7.33928571428571" style="6" customWidth="1"/>
+    <col min="11" max="12" width="5.66071428571429" style="6" customWidth="1"/>
+    <col min="13" max="13" width="8.33928571428571" style="7" customWidth="1"/>
     <col min="14" max="16384" width="12" style="5"/>
   </cols>
   <sheetData>
@@ -2927,7 +2799,7 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="2" s="1" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -2940,7 +2812,7 @@
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="3" s="1" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2985,9 +2857,7 @@
       <c r="J5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="67" t="s">
-        <v>5</v>
-      </c>
+      <c r="K5" s="22"/>
       <c r="L5" s="22"/>
       <c r="M5" s="23"/>
     </row>
@@ -2995,7 +2865,7 @@
       <c r="A6" s="14"/>
       <c r="B6" s="15"/>
       <c r="C6" s="16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="18"/>
@@ -3026,40 +2896,38 @@
     <row r="8" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A8" s="30"/>
       <c r="B8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="D8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="E8" s="32" t="s">
         <v>9</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>10</v>
       </c>
       <c r="F8" s="32"/>
       <c r="G8" s="33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" s="33"/>
       <c r="I8" s="34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" s="34"/>
       <c r="K8" s="34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L8" s="34"/>
       <c r="M8" s="23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A9" s="23"/>
       <c r="B9" s="18"/>
-      <c r="C9" s="35" t="s">
-        <v>15</v>
-      </c>
+      <c r="C9" s="35"/>
       <c r="D9" s="23"/>
       <c r="E9" s="36"/>
       <c r="F9" s="29"/>
@@ -3075,7 +2943,7 @@
       <c r="A10" s="23"/>
       <c r="B10" s="37"/>
       <c r="C10" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" s="39"/>
       <c r="E10" s="40"/>
@@ -3090,34 +2958,18 @@
     </row>
     <row r="11" s="2" customFormat="1" ht="51" customHeight="1" spans="1:14">
       <c r="A11" s="23"/>
-      <c r="B11" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>20</v>
-      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
       <c r="F11" s="40"/>
-      <c r="G11" s="44" t="s">
-        <v>21</v>
-      </c>
+      <c r="G11" s="44"/>
       <c r="H11" s="45"/>
-      <c r="I11" s="44" t="s">
-        <v>21</v>
-      </c>
+      <c r="I11" s="44"/>
       <c r="J11" s="45"/>
-      <c r="K11" s="44" t="s">
-        <v>21</v>
-      </c>
+      <c r="K11" s="44"/>
       <c r="L11" s="45"/>
-      <c r="M11" s="44" t="s">
-        <v>21</v>
-      </c>
+      <c r="M11" s="44"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A12" s="23"/>
@@ -3125,36 +2977,36 @@
         <v>4500028983</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E12" s="46">
         <v>96</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G12" s="41">
         <f>38.59+3</f>
         <v>41.59</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I12" s="42">
         <f>45.4+3.3</f>
         <v>48.7</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K12" s="42">
         <v>0.31</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M12" s="46">
         <v>6</v>
@@ -3166,34 +3018,34 @@
         <v>4500028983</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E13" s="46">
         <v>262</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G13" s="41">
         <v>117.67</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I13" s="41">
         <v>138.43</v>
       </c>
       <c r="J13" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K13" s="42">
         <v>0.78</v>
       </c>
       <c r="L13" s="46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M13" s="46">
         <v>15</v>
@@ -3206,36 +3058,36 @@
         <v>4500028983</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E14" s="46">
         <v>292</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G14" s="41">
         <f>136.41+2.01</f>
         <v>138.42</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I14" s="41">
         <f>160.48+2.6</f>
         <v>163.08</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K14" s="42">
         <v>0.83</v>
       </c>
       <c r="L14" s="46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M14" s="46">
         <v>16</v>
@@ -3248,34 +3100,34 @@
         <v>4500028983</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E15" s="46">
         <v>132</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G15" s="41">
         <v>101.35</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I15" s="41">
         <v>119.24</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K15" s="42">
         <v>0.58</v>
       </c>
       <c r="L15" s="46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M15" s="46">
         <v>11</v>
@@ -3288,37 +3140,37 @@
         <v>4500028983</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E16" s="46">
         <v>425</v>
       </c>
       <c r="F16" s="46" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G16" s="41">
         <f>245.62+175.44</f>
         <v>421.06</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I16" s="42">
         <f>288.96+206.4</f>
         <v>495.36</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K16" s="42">
         <f>1.55+1.11</f>
         <v>2.66</v>
       </c>
       <c r="L16" s="46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M16" s="46">
         <v>36</v>
@@ -3331,34 +3183,34 @@
         <v>4500030322</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E17" s="46">
         <v>16</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G17" s="41">
         <v>6.77</v>
       </c>
       <c r="H17" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I17" s="41">
         <v>7.96</v>
       </c>
       <c r="J17" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K17" s="42">
         <v>0.05</v>
       </c>
       <c r="L17" s="46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M17" s="46">
         <v>1</v>
@@ -3370,34 +3222,34 @@
         <v>4500030322</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E18" s="46">
         <v>54</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G18" s="41">
         <v>24.17</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I18" s="41">
         <v>28.44</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K18" s="42">
         <v>0.16</v>
       </c>
       <c r="L18" s="46" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M18" s="46">
         <v>3</v>
@@ -3420,7 +3272,7 @@
     </row>
     <row r="20" ht="16" customHeight="1" spans="1:81">
       <c r="A20" s="54" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B20" s="27"/>
       <c r="C20" s="54"/>
@@ -3430,28 +3282,28 @@
         <v>1277</v>
       </c>
       <c r="F20" s="55" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G20" s="42">
         <f t="shared" si="0"/>
         <v>851.03</v>
       </c>
       <c r="H20" s="56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I20" s="56">
         <f t="shared" si="0"/>
         <v>1001.21</v>
       </c>
       <c r="J20" s="56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K20" s="56">
         <f>SUM(K10:K19)</f>
         <v>5.37</v>
       </c>
       <c r="L20" s="55" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M20" s="56">
         <f>SUM(M10:M19)</f>
@@ -3491,7 +3343,7 @@
     </row>
     <row r="23" s="2" customFormat="1" ht="16" customHeight="1" spans="1:81">
       <c r="A23" s="65" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B23" s="58"/>
       <c r="C23" s="65"/>
@@ -3573,15 +3425,13 @@
       <c r="CB23" s="3"/>
       <c r="CC23" s="3"/>
     </row>
-    <row r="24" ht="15.5" spans="1:81">
+    <row r="24" spans="1:81">
       <c r="A24" s="65" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B24" s="58"/>
       <c r="C24" s="65"/>
-      <c r="D24" s="66" t="s">
-        <v>38</v>
-      </c>
+      <c r="D24" s="66"/>
       <c r="E24" s="60"/>
       <c r="F24" s="61"/>
       <c r="G24" s="62"/>
@@ -3592,9 +3442,9 @@
       <c r="L24" s="57"/>
       <c r="M24" s="59"/>
     </row>
-    <row r="25" ht="15.5" spans="1:81">
+    <row r="25" spans="1:81">
       <c r="A25" s="65" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B25" s="58"/>
       <c r="C25" s="65"/>
